--- a/KatalonData/IWPBootstrapData/VRelayPaymentsACH_30.xlsx
+++ b/KatalonData/IWPBootstrapData/VRelayPaymentsACH_30.xlsx
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1379" uniqueCount="139">
   <si>
     <t>Result</t>
   </si>
@@ -291,6 +291,201 @@
   </si>
   <si>
     <t>Wed May 06 21:51:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:50:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:52:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:54:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:01:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:02:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:03:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:04:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:06:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:07:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:08:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:10:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:11:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:12:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:14:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:15:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:18:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:19:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:20:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:22:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:24:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:25:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:27:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:28:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:29:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:31:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:33:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:34:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:36:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:37:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:38:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:44:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:46:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:48:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:50:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:52:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:54:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:56:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:57:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 00:06:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 00:08:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 00:10:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 00:17:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 00:19:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 00:23:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 00:38:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 00:46:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 00:49:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 00:49:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 00:50:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 00:52:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 00:53:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 00:57:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 01:03:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 01:04:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 01:05:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 01:07:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 01:14:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 01:16:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 01:17:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 01:19:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 01:21:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 01:27:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 01:28:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 01:29:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 19:25:32 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -681,7 +876,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -775,7 +970,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -870,7 +1065,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -962,7 +1157,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1054,7 +1249,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1146,7 +1341,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>93</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1238,7 +1433,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1330,7 +1525,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1427,7 +1622,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>135</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1521,7 +1716,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>136</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1615,7 +1810,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1712,7 +1907,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1806,7 +2001,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>137</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1988,7 +2183,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>122</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2082,7 +2277,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2179,7 +2374,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2276,7 +2471,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -2369,7 +2564,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2468,7 +2663,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2564,7 +2759,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2660,7 +2855,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2754,7 +2949,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2848,7 +3043,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2939,10 +3134,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3036,7 +3231,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3130,7 +3325,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>138</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3224,7 +3419,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3412,7 +3607,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3506,7 +3701,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>123</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3701,7 +3896,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3795,7 +3990,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>124</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3891,7 +4086,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>129</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3987,7 +4182,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4083,7 +4278,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>125</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4276,7 +4471,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>102</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4370,7 +4565,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4464,7 +4659,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4558,7 +4753,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4652,7 +4847,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
